--- a/data/trans_orig/P6701-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6701-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen que trabajar muy rápido en 2012</t>
+          <t>Población según si tienen que trabajar muy rápido en 2012 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35680</t>
+          <t>35657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28909</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55040</t>
+          <t>54491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23899</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46985</t>
+          <t>45866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34028</t>
+          <t>34562</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43375</t>
+          <t>45203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73030</t>
+          <t>73994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85195</t>
+          <t>85455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117498</t>
+          <t>117055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48577</t>
+          <t>47227</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74059</t>
+          <t>73129</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>141670</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>181839</t>
+          <t>181867</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58437</t>
+          <t>59108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88133</t>
+          <t>88691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>50386</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92751</t>
+          <t>93179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129093</t>
+          <t>130629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26875</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49080</t>
+          <t>49035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14235</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32303</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>47305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75025</t>
+          <t>76177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53860</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47169</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58436</t>
+          <t>57873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94258</t>
+          <t>93313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>28137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53541</t>
+          <t>53342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20156</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40773</t>
+          <t>41894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53327</t>
+          <t>53325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86187</t>
+          <t>85816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134822</t>
+          <t>131509</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173707</t>
+          <t>172947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76925</t>
+          <t>76839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109782</t>
+          <t>108017</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>217195</t>
+          <t>218555</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>271707</t>
+          <t>269999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88022</t>
+          <t>88649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127210</t>
+          <t>125665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>49730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>78436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144893</t>
+          <t>145578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195041</t>
+          <t>194507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58775</t>
+          <t>57625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91335</t>
+          <t>89958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40035</t>
+          <t>39338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65459</t>
+          <t>67501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104920</t>
+          <t>106306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147036</t>
+          <t>146577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27112</t>
+          <t>28492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53194</t>
+          <t>54789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47178</t>
+          <t>46960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>39903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70550</t>
+          <t>69767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89926</t>
+          <t>90513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125093</t>
+          <t>127970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50183</t>
+          <t>48868</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76639</t>
+          <t>78294</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147428</t>
+          <t>148177</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>194120</t>
+          <t>196336</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>63106</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96620</t>
+          <t>96689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33358</t>
+          <t>33945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59169</t>
+          <t>59139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>105336</t>
+          <t>104891</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143756</t>
+          <t>143602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>70578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103573</t>
+          <t>105925</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50325</t>
+          <t>48778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76756</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>127379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>170151</t>
+          <t>172280</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34340</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61437</t>
+          <t>63378</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>50991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70312</t>
+          <t>69913</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108876</t>
+          <t>106742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33337</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>60581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>22730</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45364</t>
+          <t>44444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61137</t>
+          <t>61127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98941</t>
+          <t>96902</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>155752</t>
+          <t>156120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>195794</t>
+          <t>197437</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95426</t>
+          <t>93469</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>130833</t>
+          <t>128856</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>261368</t>
+          <t>263294</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>315593</t>
+          <t>315782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66232</t>
+          <t>65194</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97487</t>
+          <t>97650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48707</t>
+          <t>49526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77227</t>
+          <t>77602</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124575</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>165217</t>
+          <t>164868</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53987</t>
+          <t>53813</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>84338</t>
+          <t>84183</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43986</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71847</t>
+          <t>71563</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106267</t>
+          <t>104936</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>148178</t>
+          <t>146408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>103779</t>
+          <t>106177</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>149864</t>
+          <t>150835</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>96215</t>
+          <t>94723</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>139782</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>210001</t>
+          <t>213087</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>272739</t>
+          <t>273213</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>129198</t>
+          <t>128311</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>183170</t>
+          <t>177233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>86447</t>
+          <t>87675</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>126194</t>
+          <t>127143</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230014</t>
+          <t>230390</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296626</t>
+          <t>292399</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>497043</t>
+          <t>498003</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>575796</t>
+          <t>575729</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>294826</t>
+          <t>294209</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>355040</t>
+          <t>354222</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>817649</t>
+          <t>814509</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>911198</t>
+          <t>913659</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>304712</t>
+          <t>311380</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>372860</t>
+          <t>375891</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>181869</t>
+          <t>181745</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>232141</t>
+          <t>233995</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>505621</t>
+          <t>502125</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>590634</t>
+          <t>589543</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>238430</t>
+          <t>237949</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>294271</t>
+          <t>297914</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>171377</t>
+          <t>170509</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>221960</t>
+          <t>220108</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>423538</t>
+          <t>417124</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>501347</t>
+          <t>499761</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen que trabajar muy rápido en 2016</t>
+          <t>Población según si tienen que trabajar muy rápido en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32201</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>33619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57539</t>
+          <t>57677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42994</t>
+          <t>44049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
+          <t>43440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70402</t>
+          <t>72200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84308</t>
+          <t>83451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114877</t>
+          <t>113927</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49781</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73356</t>
+          <t>72147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141709</t>
+          <t>140875</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>178512</t>
+          <t>178437</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53432</t>
+          <t>54229</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83012</t>
+          <t>82250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>55996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>93334</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131719</t>
+          <t>129961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>16096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23716</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27697</t>
+          <t>28579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52669</t>
+          <t>53732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46441</t>
+          <t>46610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21616</t>
+          <t>21639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41545</t>
+          <t>42628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49137</t>
+          <t>48662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80312</t>
+          <t>79549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40570</t>
+          <t>41366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69343</t>
+          <t>69906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28856</t>
+          <t>28029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51595</t>
+          <t>52053</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76214</t>
+          <t>75896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113445</t>
+          <t>112248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>125558</t>
+          <t>126768</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164328</t>
+          <t>165852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90172</t>
+          <t>91378</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122936</t>
+          <t>123798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>224211</t>
+          <t>225954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>278311</t>
+          <t>278964</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101775</t>
+          <t>98978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139880</t>
+          <t>139531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39625</t>
+          <t>39681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65427</t>
+          <t>64674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149202</t>
+          <t>149627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195857</t>
+          <t>194365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48116</t>
+          <t>47017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77372</t>
+          <t>79824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>33699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60144</t>
+          <t>59881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90531</t>
+          <t>91235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129224</t>
+          <t>131325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22551</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>44546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40740</t>
+          <t>39848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>34026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38731</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66854</t>
+          <t>64305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90513</t>
+          <t>88972</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>126880</t>
+          <t>125938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86150</t>
+          <t>86765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117785</t>
+          <t>118957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>184871</t>
+          <t>186589</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>232391</t>
+          <t>234942</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>105626</t>
+          <t>105605</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142522</t>
+          <t>142468</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56121</t>
+          <t>55410</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84541</t>
+          <t>84057</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>171695</t>
+          <t>168338</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>215309</t>
+          <t>217317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70687</t>
+          <t>72682</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105173</t>
+          <t>107634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50377</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77881</t>
+          <t>76048</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129875</t>
+          <t>128484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>174519</t>
+          <t>174025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>29106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>31119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58438</t>
+          <t>58570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70988</t>
+          <t>72130</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36193</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62862</t>
+          <t>63421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87363</t>
+          <t>86591</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>124151</t>
+          <t>124320</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133845</t>
+          <t>133776</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>172165</t>
+          <t>172937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>108393</t>
+          <t>106677</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>143836</t>
+          <t>142430</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>252848</t>
+          <t>251566</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>305133</t>
+          <t>303629</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71444</t>
+          <t>69307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103471</t>
+          <t>101741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56543</t>
+          <t>55211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86989</t>
+          <t>85754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135806</t>
+          <t>137424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181243</t>
+          <t>181011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65642</t>
+          <t>66286</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99896</t>
+          <t>97762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>48996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79605</t>
+          <t>79029</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>122787</t>
+          <t>120838</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>168686</t>
+          <t>166023</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>76656</t>
+          <t>77716</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>118542</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69364</t>
+          <t>70784</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>104390</t>
+          <t>104647</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>156974</t>
+          <t>159650</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>208762</t>
+          <t>210988</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>147480</t>
+          <t>145913</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>195721</t>
+          <t>194805</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>114529</t>
+          <t>113068</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>159562</t>
+          <t>156973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>270054</t>
+          <t>274044</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>340226</t>
+          <t>340642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>471120</t>
+          <t>469472</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>541452</t>
+          <t>540658</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>360927</t>
+          <t>362031</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>423119</t>
+          <t>425198</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>845746</t>
+          <t>849362</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>942385</t>
+          <t>948671</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>364294</t>
+          <t>363718</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>429461</t>
+          <t>431612</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>211795</t>
+          <t>210554</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>266999</t>
+          <t>264725</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>588716</t>
+          <t>589262</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>676774</t>
+          <t>675247</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>227681</t>
+          <t>226109</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>288267</t>
+          <t>286593</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>159836</t>
+          <t>161878</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>209549</t>
+          <t>210317</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>404644</t>
+          <t>402713</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>486608</t>
+          <t>479049</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen que trabajar muy rápido en 2023</t>
+          <t>Población según si tienen que trabajar muy rápido en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37499</t>
+          <t>36467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>25050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46089</t>
+          <t>44558</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18339</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32520</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43524</t>
+          <t>43561</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72848</t>
+          <t>71715</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25978</t>
+          <t>25701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49690</t>
+          <t>49522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>12992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>34751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>355119</t>
+          <t>351471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51325</t>
+          <t>50939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>429014</t>
+          <t>431587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56552</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64843</t>
+          <t>63828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171835</t>
+          <t>174533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28113</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46058</t>
+          <t>46408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>200065</t>
+          <t>200562</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,09%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100965</t>
+          <t>103240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>37064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20937</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131146</t>
+          <t>131723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57063</t>
+          <t>54568</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33791</t>
+          <t>34676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90310</t>
+          <t>92639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15150</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>33774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35012</t>
+          <t>34399</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>32312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>37606</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61713</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32247</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35762</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57654</t>
+          <t>57404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28664</t>
+          <t>27469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39869</t>
+          <t>39896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26602</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59754</t>
+          <t>60011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20750</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>31024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41647</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35599</t>
+          <t>35846</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47703</t>
+          <t>47583</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71621</t>
+          <t>71277</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18028</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54628</t>
+          <t>54893</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18079</t>
+          <t>18974</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37222</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>110204</t>
+          <t>108777</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>524786</t>
+          <t>526865</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40521</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65277</t>
+          <t>65763</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>157832</t>
+          <t>159194</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>692080</t>
+          <t>732527</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80519</t>
+          <t>80638</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33666</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54987</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44279</t>
+          <t>39496</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>128020</t>
+          <t>124611</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61171</t>
+          <t>57858</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>246825</t>
+          <t>250417</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>97147</t>
+          <t>98007</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128210</t>
+          <t>128145</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>132131</t>
+          <t>114659</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>358301</t>
+          <t>356233</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43020</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>169269</t>
+          <t>171435</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>73245</t>
+          <t>72169</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>103174</t>
+          <t>100388</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>91575</t>
+          <t>83884</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>257253</t>
+          <t>256668</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>87956</t>
+          <t>89714</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>74269</t>
+          <t>73791</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>53172</t>
+          <t>54317</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>156945</t>
+          <t>154761</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6701-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6701-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35657</t>
+          <t>35768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27259</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>28552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54491</t>
+          <t>55173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>23353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45866</t>
+          <t>46796</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>33995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>44307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73994</t>
+          <t>74167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85455</t>
+          <t>85716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117055</t>
+          <t>119078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>47089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73129</t>
+          <t>73100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141670</t>
+          <t>141654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>181867</t>
+          <t>182037</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59108</t>
+          <t>59345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88691</t>
+          <t>88839</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50386</t>
+          <t>49703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93179</t>
+          <t>92230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130629</t>
+          <t>128126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49035</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47305</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76177</t>
+          <t>74946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>29130</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54213</t>
+          <t>55182</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46255</t>
+          <t>48199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57873</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93313</t>
+          <t>97068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>27881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53342</t>
+          <t>52843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41894</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53325</t>
+          <t>53640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85816</t>
+          <t>84766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131509</t>
+          <t>132373</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>172947</t>
+          <t>172461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76839</t>
+          <t>74730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108017</t>
+          <t>108248</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218555</t>
+          <t>216819</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>269999</t>
+          <t>269201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88649</t>
+          <t>87144</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125665</t>
+          <t>127100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49730</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78436</t>
+          <t>78684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145578</t>
+          <t>146444</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194507</t>
+          <t>193050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57625</t>
+          <t>59510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89958</t>
+          <t>91278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39338</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67501</t>
+          <t>66288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106306</t>
+          <t>106566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>146577</t>
+          <t>147546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26181</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>34199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28492</t>
+          <t>27078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54789</t>
+          <t>52357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46960</t>
+          <t>48107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39903</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69767</t>
+          <t>71322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90513</t>
+          <t>91409</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127970</t>
+          <t>128702</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78294</t>
+          <t>78740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>148177</t>
+          <t>149916</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>196336</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63106</t>
+          <t>62838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96689</t>
+          <t>95394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59139</t>
+          <t>58801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104891</t>
+          <t>102259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143602</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70578</t>
+          <t>70573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105925</t>
+          <t>105897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48778</t>
+          <t>50350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>78356</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127379</t>
+          <t>130591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>172280</t>
+          <t>173755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>34966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63378</t>
+          <t>62028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50991</t>
+          <t>50968</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69913</t>
+          <t>69832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106742</t>
+          <t>106131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32784</t>
+          <t>33680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60581</t>
+          <t>61743</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>22577</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44444</t>
+          <t>44113</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61127</t>
+          <t>62042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>96902</t>
+          <t>98195</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156120</t>
+          <t>155294</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>197437</t>
+          <t>196108</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>93469</t>
+          <t>93799</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128856</t>
+          <t>128508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>263294</t>
+          <t>258310</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>315782</t>
+          <t>313771</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65194</t>
+          <t>66486</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>100419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49526</t>
+          <t>49084</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77602</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>122872</t>
+          <t>123564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>164868</t>
+          <t>166585</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53813</t>
+          <t>54349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>84183</t>
+          <t>85402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>43478</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71563</t>
+          <t>71254</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>104936</t>
+          <t>106650</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146408</t>
+          <t>146362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>106177</t>
+          <t>104603</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>150835</t>
+          <t>151165</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94723</t>
+          <t>94780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>136221</t>
+          <t>136144</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>213087</t>
+          <t>212573</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>273213</t>
+          <t>272587</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128311</t>
+          <t>128544</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>177233</t>
+          <t>178218</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87675</t>
+          <t>89267</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>127143</t>
+          <t>129341</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230390</t>
+          <t>227321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>292399</t>
+          <t>287794</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>498003</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>575729</t>
+          <t>576113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>294209</t>
+          <t>296644</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>354222</t>
+          <t>355599</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>814509</t>
+          <t>816880</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>913659</t>
+          <t>914399</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>311380</t>
+          <t>310238</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>375891</t>
+          <t>374984</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>181745</t>
+          <t>181522</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>233995</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>502125</t>
+          <t>505461</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>589543</t>
+          <t>586225</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>237949</t>
+          <t>240442</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>297914</t>
+          <t>299735</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>170509</t>
+          <t>169347</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>220108</t>
+          <t>220713</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>417124</t>
+          <t>421489</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>499761</t>
+          <t>495878</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32622</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57677</t>
+          <t>57295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>42633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>34162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>44321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72200</t>
+          <t>71435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83451</t>
+          <t>83877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113927</t>
+          <t>115076</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>49434</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72147</t>
+          <t>72453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140875</t>
+          <t>139438</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>178437</t>
+          <t>178357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54229</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82250</t>
+          <t>80750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34909</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55996</t>
+          <t>56717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93334</t>
+          <t>92930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129961</t>
+          <t>128784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>17255</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28579</t>
+          <t>27811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53732</t>
+          <t>51513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22111</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46610</t>
+          <t>45533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21639</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>41080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48662</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79549</t>
+          <t>82480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>41146</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69906</t>
+          <t>68315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>27209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52053</t>
+          <t>51487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75896</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112248</t>
+          <t>110901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126768</t>
+          <t>126772</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>165852</t>
+          <t>165401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91378</t>
+          <t>89271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123798</t>
+          <t>123333</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225954</t>
+          <t>229530</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>278964</t>
+          <t>279312</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98978</t>
+          <t>101594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139531</t>
+          <t>139309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64674</t>
+          <t>65394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149627</t>
+          <t>151106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194365</t>
+          <t>194932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47017</t>
+          <t>47444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79824</t>
+          <t>77279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33699</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59881</t>
+          <t>59825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91235</t>
+          <t>88751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131325</t>
+          <t>129686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>28909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22566</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44546</t>
+          <t>45183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34026</t>
+          <t>33127</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38690</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64305</t>
+          <t>65154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88972</t>
+          <t>89714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125938</t>
+          <t>125222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86765</t>
+          <t>86854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118957</t>
+          <t>118558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>186589</t>
+          <t>185413</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>234942</t>
+          <t>236347</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>105605</t>
+          <t>104103</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142468</t>
+          <t>140812</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55410</t>
+          <t>55296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84057</t>
+          <t>83089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168338</t>
+          <t>169716</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>217317</t>
+          <t>216433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72682</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107634</t>
+          <t>105363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49034</t>
+          <t>49713</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76048</t>
+          <t>77275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128484</t>
+          <t>129007</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>174025</t>
+          <t>172417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>35202</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>29747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58570</t>
+          <t>57591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43866</t>
+          <t>43796</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72130</t>
+          <t>71300</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36156</t>
+          <t>35445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63421</t>
+          <t>61718</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>86591</t>
+          <t>84819</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>124320</t>
+          <t>124112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133776</t>
+          <t>133994</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>172937</t>
+          <t>173232</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>106677</t>
+          <t>107317</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>142430</t>
+          <t>143399</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>251566</t>
+          <t>252276</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>303629</t>
+          <t>304184</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69307</t>
+          <t>72175</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101741</t>
+          <t>104847</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>57532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85754</t>
+          <t>86637</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137424</t>
+          <t>137240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181011</t>
+          <t>182300</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66286</t>
+          <t>65177</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97762</t>
+          <t>98578</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>49383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79029</t>
+          <t>77430</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>120838</t>
+          <t>122110</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>166023</t>
+          <t>166887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>77716</t>
+          <t>77469</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118542</t>
+          <t>116248</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>70784</t>
+          <t>69596</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>104647</t>
+          <t>103551</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>159650</t>
+          <t>155540</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>210988</t>
+          <t>206855</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>145913</t>
+          <t>145513</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>194805</t>
+          <t>194376</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>113068</t>
+          <t>115524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156973</t>
+          <t>157219</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>274044</t>
+          <t>270546</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>340642</t>
+          <t>341471</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>469472</t>
+          <t>471053</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>540658</t>
+          <t>544442</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>362031</t>
+          <t>362912</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>425198</t>
+          <t>425135</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>849362</t>
+          <t>851334</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>948671</t>
+          <t>948380</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>363718</t>
+          <t>361140</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>431612</t>
+          <t>430832</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>210554</t>
+          <t>209121</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>264725</t>
+          <t>261341</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>589262</t>
+          <t>587454</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>675247</t>
+          <t>674931</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>226109</t>
+          <t>226467</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>286593</t>
+          <t>289912</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>161878</t>
+          <t>162043</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>210317</t>
+          <t>212020</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>402713</t>
+          <t>404177</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>479049</t>
+          <t>483519</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26785</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>16703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,32 +8194,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25050</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31525</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>25169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44558</t>
+          <t>47768</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>35342</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56627</t>
+          <t>61925</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43561</t>
+          <t>48284</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71715</t>
+          <t>76869</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32649</t>
+          <t>36293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>28393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49522</t>
+          <t>54953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>28546</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36809</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>260233</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>351471</t>
+          <t>31913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20858</t>
+          <t>25913</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>274530</t>
+          <t>37458</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50939</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>431587</t>
+          <t>51090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>19793</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58159</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>31893</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63828</t>
+          <t>45162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63573</t>
+          <t>69627</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>55337</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174533</t>
+          <t>84462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36257</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46408</t>
+          <t>49884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>99829</t>
+          <t>109437</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32267</t>
+          <t>93878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>200562</t>
+          <t>127798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>29284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103240</t>
+          <t>54727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>32235</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37064</t>
+          <t>40746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63992</t>
+          <t>72827</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>60103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131723</t>
+          <t>89302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>21497</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54568</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>44234</t>
+          <t>48532</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>35931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92639</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>22114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>25417</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32735</t>
+          <t>37506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>23901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33774</t>
+          <t>37180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34399</t>
+          <t>41302</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24494</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17451</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32312</t>
+          <t>36970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>49101</t>
+          <t>58450</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37606</t>
+          <t>45592</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60955</t>
+          <t>72624</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30045</t>
+          <t>34872</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>37037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>46016</t>
+          <t>53009</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>40343</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57404</t>
+          <t>66377</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>26660</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>19550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>23589</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27469</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>31918</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>42538</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>19902</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>12938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47584</t>
+          <t>51820</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36745</t>
+          <t>39460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60011</t>
+          <t>64489</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31024</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31233</t>
+          <t>32281</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42132</t>
+          <t>42989</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27618</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>58851</t>
+          <t>60875</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47583</t>
+          <t>49128</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71277</t>
+          <t>74481</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>30775</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37061</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>26338</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>42231</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31658</t>
+          <t>37453</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54893</t>
+          <t>62548</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>23620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20708</t>
+          <t>23519</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>30531</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18974</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37234</t>
+          <t>41609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>318468</t>
+          <t>82760</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>108777</t>
+          <t>65848</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>526865</t>
+          <t>101714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40616</t>
+          <t>47129</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65763</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>370630</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>159194</t>
+          <t>119194</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>732527</t>
+          <t>163398</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>47114</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>36788</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80638</t>
+          <t>67304</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>46807</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54210</t>
+          <t>59893</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>80705</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>124611</t>
+          <t>119923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>150938</t>
+          <t>166905</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57858</t>
+          <t>143810</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>250417</t>
+          <t>191138</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>113470</t>
+          <t>123782</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>98007</t>
+          <t>108756</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128145</t>
+          <t>140318</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>264409</t>
+          <t>290687</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114659</t>
+          <t>263785</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>356233</t>
+          <t>320503</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>102200</t>
+          <t>116652</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>95775</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>171435</t>
+          <t>137264</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>86213</t>
+          <t>98325</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>72169</t>
+          <t>82594</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>100388</t>
+          <t>113990</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>188413</t>
+          <t>214977</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>83884</t>
+          <t>187777</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>256668</t>
+          <t>240996</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>46988</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>89714</t>
+          <t>86359</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>60572</t>
+          <t>67549</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>47664</t>
+          <t>53855</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>73791</t>
+          <t>82070</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>111975</t>
+          <t>131199</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>54317</t>
+          <t>108694</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>154761</t>
+          <t>157239</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
